--- a/ASBL_Data_Template.xlsx
+++ b/ASBL_Data_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nsain\Documents\Service_cost_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99D4B72-04E8-463A-864D-2D1D1D66BB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183AA76F-5277-4F9F-A830-2AA955EB74C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ASBL_Data_Template" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ASBL_Data_Template!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ASBL_Data_Template!$C$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -387,32 +387,30 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="C1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>